--- a/args edit.xlsx
+++ b/args edit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{EA23FE03-A756-420D-B1C8-66EF0690EA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{666A4E7A-1590-4D5E-B932-A84F361D62BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="631" uniqueCount="532">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="745" uniqueCount="624">
   <si>
     <t>__v</t>
   </si>
@@ -1680,6 +1680,282 @@
   </si>
   <si>
     <t>Teacher Re-education</t>
+  </si>
+  <si>
+    <t>O0059</t>
+  </si>
+  <si>
+    <t>The aim for all of us should be towards developing dual-­use platforms with a special focus towards incorporating cutting­ edge technology and we must expand our NAVIC constellation, provide agile space-based Intelligence, Surveillance and Reconnaissance (ISR) and ensure secure satellite­ assisted communications. The populating of the space domain and the emergence of a dynamic threat environment to our space assets also demand that we enhance our space situational awareness capability. There’s also a requirement to safeguard our assets with counter space capabilities. We must build resilience and redundancy in a space-based infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#CHIEF_OF_DEFENCE_STAFF </t>
+  </si>
+  <si>
+    <t>On militarisation of space</t>
+  </si>
+  <si>
+    <t>O0060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are two issues in the creation of a single platform for coordinating the appointment process in Central Universities. Central universities are established under the Acts of Parliament. Step by step, the government is ending the autonomous nature of these varsities. Second, we fear there is a ploy to rig the appointments of faculty members by the ruling party. </t>
+  </si>
+  <si>
+    <t>#ACADEMIC_ASSOCIATIONS</t>
+  </si>
+  <si>
+    <t>On academic freedom</t>
+  </si>
+  <si>
+    <t>Disaster Management</t>
+  </si>
+  <si>
+    <t>S0017</t>
+  </si>
+  <si>
+    <t>IMD has forecasted a “normal” monsoon with rainfall at 96% (with an error margin of +/-5%) of the long-period average (LPA) for 2023.</t>
+  </si>
+  <si>
+    <t>In recent years, the IMD has started to place greater emphasis on the ‘dynamical’ monsoon forecast techniques where global atmospheric and ocean conditions are simulated on powerful supercomputers to forecast climate conditions. This is different from the traditional, statistical approach where 8-10 meteorological factors, such as Eurasian snow cover and Arabian Sea surface, are correlated to the monsoon rainfall in past years to forecast a coming year’s monsoon.</t>
+  </si>
+  <si>
+    <t>From 1951-2022, there have been 15 ‘El Nino’ years, defined as a greater-than-half-degree Celsius rise in temperatures in the central, equatorial Pacific Ocean with nine of those years witnessing ‘below normal’ rains. In 2015, the last ‘strong’ El Nino year (&gt;1.5 C rise), monsoon rains shrivel by 14%. A ‘weaker’ El Nino (a sub-1C rise) in 2018 saw a contraction of 7.4%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ‘El Nino’ is only likely to begin to take root in the second half of the monsoon season – August and September. The weather models also indicate the development of a ‘positive’ phase of the Indian Ocean Dipole (IOD, or warmer temperatures in the Arabian Sea and hence more moisture and rainfall over India) during these months and so, a somewhat reduced impact of the ‘El Nino’. Another factor that could blunt the ‘El Nino’ is reduced snow cover in Eurasia.</t>
+  </si>
+  <si>
+    <t>S0018</t>
+  </si>
+  <si>
+    <t>The is a growing demand for delicensing 6GHz spectrum allocation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newer WiFi routers in India largely use spectrum on two bands, sometimes simultaneously: 2.4GHz and 5GHz. As frequency increases, the range of the signal drops, but the bandwidth goes up significantly. </t>
+  </si>
+  <si>
+    <t>The WiFi 6E standard, launched in 2020, uses 6 GHz, enabling speeds upwards of 9.6 gigabits per second (Gbps). No home internet provider currently offers those speeds in India, but 6GHz spectrum supports multiple devices on a wireless network more harmoniously than in the 5GHz band, even on slower connections, enticing telecom providers and ISPs.</t>
+  </si>
+  <si>
+    <t>It is expected that 6 GHz delicensing would benefit fixed-line broadband providers and software giants, as some of the latter try to get into the public WiFi hotspot space. 6 GHz spectrum is currently reserved for mobile and satellite telecommunications, according to the National Frequency Allocation Plan, 2022.</t>
+  </si>
+  <si>
+    <t>S0019</t>
+  </si>
+  <si>
+    <t>India is working with G20 to address issues related to debt distress affecting middle­- income countries.</t>
+  </si>
+  <si>
+    <t>Three countries in India’s neighbourhood - Sri Lanka, Pakistan and Bangladesh - have sought help from the IMF.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G20’s debt restructuring process, the 2020 Common Framework, which has largely catered to poor countries, has been slow to act, with just four countries (namely Chad, Zambia, Ethiopia and Ghana) to date having applied for debt restructuring through the framework. </t>
+  </si>
+  <si>
+    <t>China, which is a major creditor country for low­- income countries have been blamed for not playing ball on the issue of debt restructuring.</t>
+  </si>
+  <si>
+    <t>Economic Empowerment through Skill Development Schemes for SCs, OBCs, DNTs and EBCs</t>
+  </si>
+  <si>
+    <t>T0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Targeted welfare assistance is a type of government program that provides financial or other forms of support to specific groups of people who are in need. This can include things like food stamps or other forms of assistance for low-income families, disability benefits for individuals who are unable to work, or housing assistance for homeless individuals or families. Unlike universal welfare programs, which provide benefits to all members of society, targeted welfare assistance is designed to provide support to specific groups of people who are deemed to be in need. Targeted welfare tends to provoke resentment among 'non-needy' about how their tax money is being frittered away in 'freebies'. </t>
+  </si>
+  <si>
+    <t>Targeted welfare assistance</t>
+  </si>
+  <si>
+    <t>Safeguarding citizens’ rights and prevention of misuse of social/online news media platforms including special emphasis on women security in the digital space</t>
+  </si>
+  <si>
+    <t>T0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geo-blocking refers to the practice of restricting online cross-border sales based on nationality, residence or place of establishment. Geo-blocking practices include denying access to websites from specified geographical locations, and/or in situations where access to a website is granted, the consumer is prevented from finalising the purchase or is asked to pay with a debit or credit card from a certain country. A consequence of Geo-blocking is the fragmentation of markets. In the copyright context, Geo-blocking has become a necessary tool for content providers that offer audio-visual (or other forms of) content in which copyright subsists, so that such content providers are assured that their services are not consumed in breach of their licence agreements. </t>
+  </si>
+  <si>
+    <t>Geo-blocking</t>
+  </si>
+  <si>
+    <t>On the need for an external monitoring mechanism for police personnel</t>
+  </si>
+  <si>
+    <t>Police Training, Modernisation and Reforms</t>
+  </si>
+  <si>
+    <t>O0061</t>
+  </si>
+  <si>
+    <t>There were 478 custodial deaths reported in Tamil Nadu between 2016­-17 and 2021­-22 and no arrests, charge sheets or convictions in the period. Following the 1986 case of D.K. Basu vs West Bengal, the Supreme Court issued 11 guidelines to accompany Article 22(1). According to them, a Magistrate should ask the accused whether he has a medical problem, caused by the police. They generally don’t ask and write “no complaints”, meaning the accused never said anything. In America, such a wrongful procedure leads to a mistrial. But, in India, when the police do something illegal, it does not vitiate the outcome of the trial. Even if they illegally enter your house and find contraband, they can charge sheet it. So when an illegality takes place, all that you may get is bail or compensation. Beyond that, we do not have a mechanism by which these officers can be taken to task. In the U.S., you can sue the police for civil damage, we can’t do that here. There is no external check, it is through the mechanisms of the government you are trying to supervise them. The police also come up with new theories to get over the law. We don’t have an institutional form of human rights organisation which can continuously fight. Secondly, there must be civilian supervision in police stations and if something happens they can visit. So monitoring should be legalised by civil society in some form.</t>
+  </si>
+  <si>
+    <t>#JUSTICE_K_CHANDRU</t>
+  </si>
+  <si>
+    <t>O0062</t>
+  </si>
+  <si>
+    <t>The Lokpal and Lokayuktas and other related law (Amendment) Bill, 2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lok Ayukta cannot investigate matters relating to the selection of candidates by political parties for contesting elections. selection of candidates was an internal affair of the political party and the party selected its candidates as per its constitution, political principles, policies, winnability, etc. Once the candidate is set up by the political party, then, on the date of the poll, the public exercise their electoral right for any of the candidates in the fray. Therefore, we are unable to subscribe to the view of the Lok Ayukta that the selection of a candidate by a political party is a matter in which the public or the community at large has an interest. </t>
+  </si>
+  <si>
+    <t>#KERALA_HIGH_COURT</t>
+  </si>
+  <si>
+    <t>On public scrutiny of intra-party democracy</t>
+  </si>
+  <si>
+    <t>Promotion of Education amongst the Weaker Sections of Minorities by Minority Educational Institutions with particular reference to Maulana Azad Education Foundation (MAEF)</t>
+  </si>
+  <si>
+    <t>O0063</t>
+  </si>
+  <si>
+    <t>Karnataka government's March 27 order scrapping the 4% OBC quota for Muslims and dividing it between Vokkaliga and Lingayat communities in the State is based on “absolutely fallacious assumptions”. For a very long period, Muslims have been treated as a ‘more backward’ community. They were sandwiched somewhere between the ‘most backward’ and ‘backward’ communities. The State had removed Muslims from the backward class list and included them under the Economically Weaker Sections (EWS) category without any empirical data collected or study done to support the move. The order was based on an “interim” report from the Karnataka State Backward Classes Commission.</t>
+  </si>
+  <si>
+    <t>#COURTROOM_DEBATES</t>
+  </si>
+  <si>
+    <t>On inclusion of Muslims under Economically Weaker Sections</t>
+  </si>
+  <si>
+    <t>O0064</t>
+  </si>
+  <si>
+    <t>Rain Water Harvesting in India</t>
+  </si>
+  <si>
+    <t>The Business Standard</t>
+  </si>
+  <si>
+    <t>On prediction of 'normal' monsoon and El Nino conditions</t>
+  </si>
+  <si>
+    <t>Even deficient rainfall, if evenly distributed, can prove more rewarding than ill-distributed normal or above-normal rainfall. Actually, only a fraction of the total rainwater is utilised for agriculture and other purposes or is conserved in the surface and underground water aquifers. The bulk of it flows down wastefully to the seas, eroding the precious soil in its wake. For the economy, a normal monsoon is vital for several reasons. Nearly 52 per cent of the country’s farmland relies wholly on rainfall for crop production, and agricultural income is a key determinant of rural demand for industrial goods and services. Robust growth in agriculture is imperative also to rein in food inflation, which had remained elevated for some time. It ruled at 5.95 per cent in February 2023 before softening to 4.79 per cent in March. Food prices account for over 40 per cent of the consumer price index. That apart, monsoon rainfall, which comprises over 70 per cent of the country’s annual precipitation, is critical for refilling the reservoirs to meet the lean-season requirement of water for irrigation and hydropower production.</t>
+  </si>
+  <si>
+    <t>O0065</t>
+  </si>
+  <si>
+    <t>It is being argued that the surge suggests Covid is becoming endemic in India and that the number of cases will continue to rise rapidly before subsiding. Even if this were correct, health administrations need to stay on high alert. If Covid is here to stay, the government urgently needs to consider a permanent strategy rather than one-off diktats to deal with the virus. Given India’s congested cities and the high proportion of diabetic and heart patients and undernourished people in the country, the population’s vulnerability to the virus will always be high. Reinfections, even if not fatal, can progressively weaken the immune and respiratory systems. These imply undesirable public-health outcomes with implications for economic prospects. Also, as a large proportion of the population will likely lack the ability to pay for such tests, free or subsidised testing facilities could be made available at public-health centres for poorer patients.</t>
+  </si>
+  <si>
+    <t>On normalising Covid response</t>
+  </si>
+  <si>
+    <t>O0066</t>
+  </si>
+  <si>
+    <t>More than 20 lakh cybercrime complaints have been registered on cybercrime.gov.in. India, according to reports, ranks third in the world in cybercrimes. The issue, police officials admit, is that many of the cybercrimes are transnational and significantly, the criminals are taking advantage of the ‘institutional inability’ to steal data and commit other frauds. The Centre has the Indian Computer Emergency Response Team and the National Critical Information Infrastructure Protection Centre. Following the ransomware attack on AlIMS last year that paralysed it for six days, the National Counter Ransomware Task Force was set up. However, not many states are equipped enough. Telangana is an exception with its state-of-the-art integrated command control centre, where a new State Cyber Security Bureau is being set up. Besides, it also has a Centre of Excellence dedicated to strengthening cybersecurity. Nonetheless, the state saw over a 100% spike in cybercrimes from 2020 to 2021. The Telangana State Police has recently unearthed a cybercrime of such magnitude that it could only be termed the country’s biggest ever.</t>
+  </si>
+  <si>
+    <t>On building infrastructure to handle cybercrime cases</t>
+  </si>
+  <si>
+    <t>Introduction of High Speed Trains</t>
+  </si>
+  <si>
+    <t>O0067</t>
+  </si>
+  <si>
+    <t>The Tribune</t>
+  </si>
+  <si>
+    <t>Railways had become an ‘arena of politics’ and its modernisation was affected by political considerations. The advancements and gains in this vital sector have been incrementalsuccessive dispensations have made their contribution over the decades. The Chennai-based Integral Coach Factory (ICF), Vande Bharat’s designer and manufacturer, was inaugurated by the then Prime Minister Nehru in 1955. The Rail Coach Factory, Kapurthala, was established in 1985, while state-of-the-art coach manufacturing units have come up in Raebareli, Latur and Sonepat in the past decade and a half. It is laudable that the ICF is spearheading the export of rail coaches and coach components to several countries in Asia and Africa, including Thailand, Myanmar, Sri Lanka, Taiwan, Zambia, Tanzania and Uganda. The Chennai factory has also made air-conditioned new-generation rakes for Kolkata Metro.</t>
+  </si>
+  <si>
+    <t>On politicisation of railways</t>
+  </si>
+  <si>
+    <t>O0068</t>
+  </si>
+  <si>
+    <t>Solid Waste Management</t>
+  </si>
+  <si>
+    <t>The story common to Ludhiana, Muktsar and Chandigarh is that sewage treatment plants (STPs) set up for the benefit of these cities are either not functioning or are ineffective. Ludhiana is bearing the brunt of inadequately treated effluents of dye-making and electroplating industries seeping into the Buddha Nullah as the STPs have not been upgraded. Farmers’ fields receive polluted irrigation water from the nullah; and since it empties into the Sutlej, the river is also polluted. Luckily, there is an Rs 840-crore rejuvenation project of the nullah going on since 2020. In contrast, Muktsar’s condition is despairing. All three STPs installed in the town have been lying defunct for almost six years. Government efforts to repair them have been rebuffed nine times as tenders floated for the purpose drew no takers. The bane of Chandigarh is the absence of any STP in Nayagaon, a Mohali village on its periphery. It is linked to the ‘Patiala ki Rao’, a choe running through the city, having deteriorated into a ‘ganda nullah’ as untreated sewage and garbage from the surrounding villages are being dumped into it.</t>
+  </si>
+  <si>
+    <t>On sewage treatment plants in Punjab</t>
+  </si>
+  <si>
+    <t>Prison Condition, Infrastructure and Reforms</t>
+  </si>
+  <si>
+    <t>O0069</t>
+  </si>
+  <si>
+    <t>The Asian Age</t>
+  </si>
+  <si>
+    <t>Legislatures pass special laws to empower the state to address certain situations where the existing common laws may be toothless. The National Security Act of 1980, was one such law that was brought in to keep preventive custody of persons who could act prejudicial to the defence of India, its relations with foreign powers, national security, public order or the maintenance of supplies and services essential to the community. Yet, NSA is not the first piece of legislation which governments invoke at their convenience to penalise people through the process of the law. The sedition law used to be a favourite tool of the government to drag its critics in court cases; it required a forceful intervention by the Supreme Court to stop the abuse of the British-era law. Two other special laws-the Unlawful Activities (Prevention) Act, 1967, and the Prevention of Money Laundering Act, 2002which make it extremely tough for the courts to grant bail to an accusedhave also been used by the governments to lock people inside for long durations. “Bail is the norm, jail is an exception” is the dictum that most democracies follow, and nothing stops India from following it.</t>
+  </si>
+  <si>
+    <t>On misuse of acts for political vendetta</t>
+  </si>
+  <si>
+    <t>Schemes for Educational and Economic empowerment of Tribals</t>
+  </si>
+  <si>
+    <t>S0022</t>
+  </si>
+  <si>
+    <t>The Indian Express</t>
+  </si>
+  <si>
+    <t>Kudmis of the Chota Nagpur plateau are demanding for being included as Scheduled Tribes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Kudmis of the Chota Nagpur plateau were counted among Scheduled Tribes under the British but were excluded from the list in independent India. </t>
+  </si>
+  <si>
+    <t>Some affluent Kudmis wanted to elevate their status as Kshatriya in the Hindu caste hierarchy and this resulted in them not being excluded from the Scheduled Tribe list prepared in 1950.</t>
+  </si>
+  <si>
+    <t>Kudmis are mainly a peasant community, with their population concentrated in the Junglemahal areas or the Chota Nagpur plateau of West Bengal, Jharkhand and Odisha. Some Kudmis are also found in Assam and northern West Bengal, who have migrated from the Chota Nagpur plateau region.</t>
+  </si>
+  <si>
+    <t>S0020</t>
+  </si>
+  <si>
+    <t>Skill Development vis-à-vis Manufacturing and Upgradation in Textiles Sector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM Mega Integrated Textile Regions and Apparel (PM MITRA) scheme aims to set up seven mega textile parks. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">These mega parks will be of at least 1,000 acres. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% of the parks will be used for developing core infrastructure. There will be common facilities and special facilities such as testing, skills training and logistical arrangements. Commercial areas will be allowed in 10%. The master developer will conceptualise and prepare the plan for the development of the park comprising these elements. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first two parks will be established in Karnataka and Tamil Nadu. </t>
+  </si>
+  <si>
+    <t>The Juvenile Justice (Care and Protection of Children) Bill, 2014</t>
+  </si>
+  <si>
+    <t>S0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tamil Nadu government has constituted a one­-man committee, headed by retired Madras High Court judge K. Chandru, to recommend measures for the effective administration of homes functioning as per the Juvenile Justice (Care and Protection of Children) Act of 2015. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The committee was requested to assess the practices with respect to admission, internment and discharge of inmates in those homes and submit its recommendations. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The committee was also requested to assess the infrastructure and amenities and make recommendations regarding their adequacy and maintenance. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarly, recommendations were called for with respect to health and medical facilities, training and capacity building, food and nutrition, requirement and qualification of staff, stakeholder participation, aftercare issues and the necessity or otherwise with respect to amending the existing legal provisions. </t>
+  </si>
+  <si>
+    <t>The committee has been requested to submit its report within four months, though it could be extended up to six months as well.</t>
   </si>
 </sst>
 </file>
@@ -2177,7 +2453,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2186,6 +2462,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2541,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X89"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.21875" customWidth="1"/>
@@ -6389,6 +6666,443 @@
         <v>531</v>
       </c>
     </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F90" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K90" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="L90" t="s">
+        <v>533</v>
+      </c>
+      <c r="M90" t="s">
+        <v>534</v>
+      </c>
+      <c r="N90" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F91" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K91" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="L91" t="s">
+        <v>537</v>
+      </c>
+      <c r="M91" t="s">
+        <v>538</v>
+      </c>
+      <c r="N91" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F92" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="J92" t="s">
+        <v>542</v>
+      </c>
+      <c r="K92" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="O92" t="s">
+        <v>543</v>
+      </c>
+      <c r="P92" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="J93" t="s">
+        <v>547</v>
+      </c>
+      <c r="K93" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="O93" t="s">
+        <v>548</v>
+      </c>
+      <c r="P93" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F94" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="J94" t="s">
+        <v>552</v>
+      </c>
+      <c r="K94" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="O94" t="s">
+        <v>553</v>
+      </c>
+      <c r="P94" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F95" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="K95" s="2" t="d">
+        <v>2023-04-11</v>
+      </c>
+      <c r="W95" t="s">
+        <v>558</v>
+      </c>
+      <c r="X95" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="F96" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="K96" s="2" t="d">
+        <v>2023-04-12</v>
+      </c>
+      <c r="W96" t="s">
+        <v>562</v>
+      </c>
+      <c r="X96" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="97" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F97" t="s">
+        <v>565</v>
+      </c>
+      <c r="G97" t="s">
+        <v>566</v>
+      </c>
+      <c r="I97" t="s">
+        <v>117</v>
+      </c>
+      <c r="K97" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L97" t="s">
+        <v>567</v>
+      </c>
+      <c r="M97" t="s">
+        <v>568</v>
+      </c>
+      <c r="N97" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="98" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F98" t="s">
+        <v>570</v>
+      </c>
+      <c r="G98" t="s">
+        <v>569</v>
+      </c>
+      <c r="I98" t="s">
+        <v>117</v>
+      </c>
+      <c r="K98" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L98" t="s">
+        <v>571</v>
+      </c>
+      <c r="M98" t="s">
+        <v>572</v>
+      </c>
+      <c r="N98" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="99" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F99" t="s">
+        <v>574</v>
+      </c>
+      <c r="G99" t="s">
+        <v>575</v>
+      </c>
+      <c r="I99" t="s">
+        <v>117</v>
+      </c>
+      <c r="K99" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L99" t="s">
+        <v>576</v>
+      </c>
+      <c r="M99" t="s">
+        <v>577</v>
+      </c>
+      <c r="N99" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="100" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F100" t="s">
+        <v>580</v>
+      </c>
+      <c r="G100" t="s">
+        <v>579</v>
+      </c>
+      <c r="I100" t="s">
+        <v>581</v>
+      </c>
+      <c r="K100" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L100" t="s">
+        <v>583</v>
+      </c>
+      <c r="M100" t="s">
+        <v>112</v>
+      </c>
+      <c r="N100" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="101" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F101" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" t="s">
+        <v>584</v>
+      </c>
+      <c r="I101" t="s">
+        <v>581</v>
+      </c>
+      <c r="K101" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L101" t="s">
+        <v>585</v>
+      </c>
+      <c r="M101" t="s">
+        <v>112</v>
+      </c>
+      <c r="N101" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="102" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F102" t="s">
+        <v>196</v>
+      </c>
+      <c r="G102" t="s">
+        <v>587</v>
+      </c>
+      <c r="I102" t="s">
+        <v>36</v>
+      </c>
+      <c r="K102" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L102" t="s">
+        <v>588</v>
+      </c>
+      <c r="M102" t="s">
+        <v>112</v>
+      </c>
+      <c r="N102" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="103" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F103" t="s">
+        <v>590</v>
+      </c>
+      <c r="G103" t="s">
+        <v>591</v>
+      </c>
+      <c r="I103" t="s">
+        <v>592</v>
+      </c>
+      <c r="K103" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L103" t="s">
+        <v>593</v>
+      </c>
+      <c r="M103" t="s">
+        <v>112</v>
+      </c>
+      <c r="N103" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="104" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F104" t="s">
+        <v>596</v>
+      </c>
+      <c r="G104" t="s">
+        <v>595</v>
+      </c>
+      <c r="I104" t="s">
+        <v>592</v>
+      </c>
+      <c r="K104" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L104" t="s">
+        <v>597</v>
+      </c>
+      <c r="M104" t="s">
+        <v>112</v>
+      </c>
+      <c r="N104" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="105" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F105" t="s">
+        <v>599</v>
+      </c>
+      <c r="G105" t="s">
+        <v>600</v>
+      </c>
+      <c r="I105" t="s">
+        <v>601</v>
+      </c>
+      <c r="K105" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="L105" t="s">
+        <v>602</v>
+      </c>
+      <c r="M105" t="s">
+        <v>112</v>
+      </c>
+      <c r="N105" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="106" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F106" t="s">
+        <v>612</v>
+      </c>
+      <c r="G106" t="s">
+        <v>611</v>
+      </c>
+      <c r="I106" t="s">
+        <v>117</v>
+      </c>
+      <c r="J106" t="s">
+        <v>613</v>
+      </c>
+      <c r="K106" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="O106" t="s">
+        <v>614</v>
+      </c>
+      <c r="P106" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="107" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F107" t="s">
+        <v>617</v>
+      </c>
+      <c r="G107" t="s">
+        <v>618</v>
+      </c>
+      <c r="I107" t="s">
+        <v>117</v>
+      </c>
+      <c r="J107" t="s">
+        <v>619</v>
+      </c>
+      <c r="K107" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="O107" t="s">
+        <v>620</v>
+      </c>
+      <c r="P107" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>622</v>
+      </c>
+      <c r="R107" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="108" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F108" t="s">
+        <v>604</v>
+      </c>
+      <c r="G108" t="s">
+        <v>605</v>
+      </c>
+      <c r="I108" t="s">
+        <v>606</v>
+      </c>
+      <c r="J108" t="s">
+        <v>607</v>
+      </c>
+      <c r="K108" s="4" t="d">
+        <v>2023-04-14</v>
+      </c>
+      <c r="O108" t="s">
+        <v>608</v>
+      </c>
+      <c r="P108" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>610</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/args edit.xlsx
+++ b/args edit.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6b78a08741e6628e/Desktop/serveup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{666A4E7A-1590-4D5E-B932-A84F361D62BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8_{459DAEF4-99D6-4DFF-B130-06748294875B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="args" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">args!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">args!$A$1:$X$108</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -7104,8 +7105,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X108" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692F42AF-C08A-4F9F-BF9F-72ED87D22970}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>